--- a/Outputs/Scenarios/PtX_demand_SE_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SE_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.004466517697420779</v>
       </c>
       <c r="K16" t="n">
-        <v>0.005833138430388838</v>
+        <v>0.006475259306487512</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.009721897383981397</v>
+        <v>0.0090779748230327</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>6.435495947338796e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.003888758953592559</v>
+        <v>0.003890560638442585</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006612135668584872</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03143247463308507</v>
+        <v>0.03489260992563983</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.05238745772180845</v>
+        <v>0.04891761386258395</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0003480071404518354</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02095498308872338</v>
+        <v>0.02096469165539312</v>
       </c>
     </row>
     <row r="43">
